--- a/public/downloads/rework-cost-check.xlsx
+++ b/public/downloads/rework-cost-check.xlsx
@@ -1480,16 +1480,16 @@
       </c>
       <c r="C24" s="8" t="n"/>
     </row>
-    <row r="25" ht="32" customHeight="1">
+    <row r="25" ht="46" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Blended price per million tokens (optional)</t>
+          <t>Your price per million tokens (optional)</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Optional, and blank in the Example on purpose: a blended rate depends on your provider, your tier and your own mix of input and output tokens, so nobody else can supply it. Enter yours and the two cost rows below fill in. Your own currency; no symbol is shown.</t>
+          <t>Type it in the shaded cell to the left. Everything else on this sheet is in tokens; fill this in and the two cost rows below appear. It is blank in the Example on purpose, because it is the one figure nobody else can supply: it depends on your provider, your tier and your own mix of input and output tokens. One number, not two — if input and output are priced differently, average them by the ratio your traces show. Your own currency; no symbol is shown.</t>
         </is>
       </c>
     </row>
@@ -3390,16 +3390,16 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
+    <row r="25" ht="46" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Blended price per million tokens (optional)</t>
+          <t>Your price per million tokens (optional)</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Optional, and blank in the Example on purpose: a blended rate depends on your provider, your tier and your own mix of input and output tokens, so nobody else can supply it. Enter yours and the two cost rows below fill in. Your own currency; no symbol is shown.</t>
+          <t>Type it in the shaded cell to the left. Everything else on this sheet is in tokens; fill this in and the two cost rows below appear. It is blank in the Example on purpose, because it is the one figure nobody else can supply: it depends on your provider, your tier and your own mix of input and output tokens. One number, not two — if input and output are priced differently, average them by the ratio your traces show. Your own currency; no symbol is shown.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/rework-cost-check.xlsx
+++ b/public/downloads/rework-cost-check.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Check" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="What each path means" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="How to find these numbers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Example" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="For scale" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="How to find these numbers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Example" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -259,6 +260,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -903,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1493,319 +1503,349 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Currency (optional)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>A label only, printed beside the two cost rows. Nothing is converted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>The two numbers</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Typical cost per task (tokens)</t>
         </is>
       </c>
-      <c r="C28" s="25">
+      <c r="C29" s="25">
         <f>IF(OR(OR(C5="",C6=""),SUM(N14:N20)&gt;0),"",C5+C6+SUM(O14:O20))</f>
         <v/>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Unit economics: what ONE task costs on a normal day, counting the rounds sent back.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>…times what one clean run costs</t>
         </is>
       </c>
-      <c r="C29" s="26">
-        <f>IF(OR(C28="",C5="",C5&lt;=0),"",C28/C5)</f>
-        <v/>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="C30" s="26">
+        <f>IF(OR(C29="",C5="",C5&lt;=0),"",C29/C5)</f>
+        <v/>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>A clean run is a task nothing sent back.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Typical demand at peak (tokens per minute)</t>
         </is>
       </c>
-      <c r="C30" s="27">
-        <f>IF(OR(C28="",C7=""),"",C7*C28)</f>
-        <v/>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="C31" s="27">
+        <f>IF(OR(C29="",C7=""),"",C7*C29)</f>
+        <v/>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Peak tasks per minute × the typical cost above.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>…as a share of your quota</t>
         </is>
       </c>
-      <c r="C31" s="28">
-        <f>IF(OR(C30="",C8="",C8&lt;=0),"",C30/C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="C32" s="28">
+        <f>IF(OR(C31="",C8="",C8&lt;=0),"",C31/C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Worst case per task (tokens)</t>
         </is>
       </c>
-      <c r="C32" s="25">
+      <c r="C33" s="25">
         <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(OR(C5="",C6=""),(SUM(R14:R20)&gt;0),SUM(P14:P20)&gt;0),"",C5+C6+SUM(Q14:Q20)))</f>
         <v/>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Availability: ONE task with every loop run to its cap.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>…times what one clean run costs</t>
         </is>
       </c>
-      <c r="C33" s="26">
-        <f>IF(OR((SUM(R14:R20)&gt;0),C32="",C5="",C5&lt;=0),"",C32/C5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="C34" s="26">
+        <f>IF(OR((SUM(R14:R20)&gt;0),C33="",C5="",C5&lt;=0),"",C33/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Worst case at peak (tokens per minute)</t>
         </is>
       </c>
-      <c r="C34" s="27">
-        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C32="",C7=""),"",C7*C32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="C35" s="27">
+        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C33="",C7=""),"",C7*C33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>…as a share of your quota</t>
         </is>
       </c>
-      <c r="C35" s="28">
-        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C34="",C8="",C8&lt;=0),"",C34/C8))</f>
-        <v/>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="C36" s="28">
+        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C35="",C8="",C8&lt;=0),"",C35/C8))</f>
+        <v/>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Over 100% means this workflow alone would ask for more than the pool holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>Cost per task</t>
-        </is>
-      </c>
-      <c r="C36" s="29">
-        <f>IF(OR(C28="",C25=""),"",C28*C25/1000000)</f>
-        <v/>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
+          <t>Cost per task</t>
+        </is>
+      </c>
+      <c r="C37" s="29">
+        <f>IF(OR(C29="",C25=""),"",C29*C25/1000000)</f>
+        <v/>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
           <t>Cost per 1,000 tasks</t>
         </is>
       </c>
-      <c r="C37" s="29">
-        <f>IF(C36="","",C36*1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="C38" s="29">
+        <f>IF(C37="","",C37*1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>…in</t>
+        </is>
+      </c>
+      <c r="C39" s="7">
+        <f>IF(C37="","",IF(C26="","your own currency",C26))</f>
+        <v/>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Whatever you called your currency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>The five checks</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Pass — nothing to do here.   ·   Attention — it works today, and something about it will surprise you.   ·   Fail — this is the one that stops you scaling, fix it first.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="30" t="n"/>
-      <c r="J40" s="30" t="n"/>
-      <c r="K40" s="30" t="n"/>
-    </row>
-    <row r="41" ht="76" customHeight="1">
-      <c r="A41" s="31" t="n">
+      <c r="H41" s="30" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="76" customHeight="1">
+      <c r="A42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>Every path that sends work back is listed
 A path you have not listed is spend you cannot see. Most teams count their retries and miss the judge entirely, because a judge rejection looks like normal operation rather than a failure.</t>
         </is>
       </c>
-      <c r="F41" s="33">
+      <c r="F42" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G42" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back.")))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.","")))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.",""))))</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="76" customHeight="1">
-      <c r="A42" s="31" t="n">
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Each round is costed as repeated, review and growth
 A round is three things and teams usually count only the first. The review call and the growing context are what make a judge loop expensive, and neither appears in a retry counter.</t>
         </is>
       </c>
-      <c r="F42" s="33">
+      <c r="F43" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G43" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round."))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.",""))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.","")))))</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="76" customHeight="1">
-      <c r="A43" s="31" t="n">
+    <row r="44" ht="76" customHeight="1">
+      <c r="A44" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>Every loop has a limit, a decided outcome, and an owner
 A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
         </is>
       </c>
-      <c r="F43" s="33">
+      <c r="F44" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G44" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner.")))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.","")))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.",""))))))</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="76" customHeight="1">
-      <c r="A44" s="31" t="n">
+    <row r="45" ht="76" customHeight="1">
+      <c r="A45" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>Both numbers fit: what you pay daily, and your busiest minute
 One number is not enough, because the two ways this hurts you are different. The typical cost is what you pay every day, and it decides whether the product makes money. The worst case at peak decides whether one bad minute takes the whole system down. A workflow can be fine on one and fatal on the other.</t>
         </is>
       </c>
-      <c r="F44" s="33">
-        <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
-        <v/>
-      </c>
-      <c r="G44" s="14">
-        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="76" customHeight="1">
-      <c r="A45" s="31" t="n">
+      <c r="F45" s="33">
+        <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C32="",C36=""),"Not answered",IF(C32&gt;1,"Fail",IF(AND(C32&lt;=0.8,C36&lt;=1),"Pass","Attention"))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="14">
+        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C32="",C36=""),"Peak tasks per minute and the quota are needed for this one.",IF(C32&gt;1,"Your normal load already exceeds the quota.",IF(AND(C32&lt;=0.8,C36&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C32&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C32="",C36=""),"",IF(C32&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C32&lt;=0.8,C36&lt;=1),"",IF(C32&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C32="",C36=""),"",IF(C32&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C32&lt;=0.8,C36&lt;=1),"",IF(C32&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>One token budget for the whole task, not one per call
 A task that goes round three times spends three times. A budget checked on each call sees the attempts one at a time and never sees the total, so it cannot stop a task that is running away. To do that, every round has to count against one limit that belongs to the task.</t>
         </is>
       </c>
-      <c r="F45" s="33">
-        <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
-        <v/>
-      </c>
-      <c r="G45" s="14">
-        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="52" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="F46" s="33">
+        <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C29=""),"Not answered",IF(C23&lt;C29,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"Pass",IF(C33="","Not answered","Attention"))))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
+        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C29=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C29,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C33="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C29=""),"",IF(C23&lt;C29,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"",IF(C33="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C29=""),"",IF(C23&lt;C29,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"",IF(C33="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>Your next step</t>
         </is>
       </c>
-      <c r="C47" s="6">
-        <f>IF(COUNTIF(F41:F45,"Fail")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Fail",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Fail",F41:F45,0)),IF(COUNTIF(F41:F45,"Attention")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Attention",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Attention",F41:F45,0)),"Nothing outstanding."))</f>
+      <c r="C48" s="6">
+        <f>IF(COUNTIF(F42:F46,"Fail")&gt;0,"Check "&amp;INDEX(A42:A46,MATCH("Fail",F42:F46,0))&amp;" — "&amp;INDEX(G42:G46,MATCH("Fail",F42:F46,0)),IF(COUNTIF(F42:F46,"Attention")&gt;0,"Check "&amp;INDEX(A42:A46,MATCH("Attention",F42:F46,0))&amp;" — "&amp;INDEX(G42:G46,MATCH("Attention",F42:F46,0)),"Nothing outstanding."))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="56">
-    <mergeCell ref="C47:K47"/>
+  <mergeCells count="61">
     <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="E36:K36"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E26:K26"/>
     <mergeCell ref="G43:K43"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C40:K40"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="E32:K32"/>
     <mergeCell ref="E25:K25"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E37:K37"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="C29:D29"/>
@@ -1813,38 +1853,42 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C48:K48"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E39:K39"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="D7:K7"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="E29:K29"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="E35:K35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="G45:K45"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="B42:E42"/>
+    <mergeCell ref="C39:D39"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="E31:K31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="E30:K30"/>
     <mergeCell ref="B44:E44"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="G44:K44"/>
     <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G44:K44"/>
     <mergeCell ref="D5:K5"/>
+    <mergeCell ref="G46:K46"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="A14:K20">
@@ -1852,15 +1896,15 @@
       <formula>$B14&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F45">
+  <conditionalFormatting sqref="F42:F46">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$F41="Pass"</formula>
+      <formula>$F42="Pass"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$F41="Attention"</formula>
+      <formula>$F42="Attention"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>$F41="Fail"</formula>
+      <formula>$F42="Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2404,6 +2448,151 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>For scale: frontier rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>What one typical task on the Check tab would cost at what three frontier models charge. It is a range because input and output are priced differently: the low figure is all input, the high figure is all output, and real work sits between them, usually nearer the low end. Figures are US dollars. Checked 28 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Input per 1M</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Output per 1M</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>Your typical task</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>Worth knowing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Claude Opus 5.5
+Anthropic</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="37">
+        <f>IF('Check'!C29="","—",TEXT('Check'!C29*C5/1000000,"0.00")&amp;" – "&amp;TEXT('Check'!C29*D5/1000000,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="38" t="inlineStr">
+        <is>
+          <t>US-only inference costs 1.1×. Fast mode costs 2×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra
+OpenAI</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="37">
+        <f>IF('Check'!C29="","—",TEXT('Check'!C29*C6/1000000,"0.00")&amp;" – "&amp;TEXT('Check'!C29*D6/1000000,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="38" t="inlineStr">
+        <is>
+          <t>Long context costs $20 in and $75 out, so a growing redo can double this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Pro
+Google</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="37">
+        <f>IF('Check'!C29="","—",TEXT('Check'!C29*C7/1000000,"0.00")&amp;" – "&amp;TEXT('Check'!C29*D7/1000000,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>Prompts over 200k cost $4 in and $18 out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Rates change, and two of these carry a condition that doubles them. Check the provider before you quote one: https://claude.com/pricing  ·  https://developers.openai.com/api/docs/pricing  ·  https://ai.google.dev/gemini-api/docs/pricing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2757,13 +2946,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3403,319 +3592,349 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Currency (optional)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>A label only, printed beside the two cost rows. Nothing is converted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>The two numbers</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Typical cost per task (tokens)</t>
         </is>
       </c>
-      <c r="C28" s="25">
+      <c r="C29" s="25">
         <f>IF(OR(OR(C5="",C6=""),SUM(N14:N20)&gt;0),"",C5+C6+SUM(O14:O20))</f>
         <v/>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Unit economics: what ONE task costs on a normal day, counting the rounds sent back.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>…times what one clean run costs</t>
         </is>
       </c>
-      <c r="C29" s="26">
-        <f>IF(OR(C28="",C5="",C5&lt;=0),"",C28/C5)</f>
-        <v/>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="C30" s="26">
+        <f>IF(OR(C29="",C5="",C5&lt;=0),"",C29/C5)</f>
+        <v/>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>A clean run is a task nothing sent back.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Typical demand at peak (tokens per minute)</t>
         </is>
       </c>
-      <c r="C30" s="27">
-        <f>IF(OR(C28="",C7=""),"",C7*C28)</f>
-        <v/>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="C31" s="27">
+        <f>IF(OR(C29="",C7=""),"",C7*C29)</f>
+        <v/>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Peak tasks per minute × the typical cost above.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>…as a share of your quota</t>
         </is>
       </c>
-      <c r="C31" s="28">
-        <f>IF(OR(C30="",C8="",C8&lt;=0),"",C30/C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="C32" s="28">
+        <f>IF(OR(C31="",C8="",C8&lt;=0),"",C31/C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Worst case per task (tokens)</t>
         </is>
       </c>
-      <c r="C32" s="25">
+      <c r="C33" s="25">
         <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(OR(C5="",C6=""),(SUM(R14:R20)&gt;0),SUM(P14:P20)&gt;0),"",C5+C6+SUM(Q14:Q20)))</f>
         <v/>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Availability: ONE task with every loop run to its cap.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>…times what one clean run costs</t>
         </is>
       </c>
-      <c r="C33" s="26">
-        <f>IF(OR((SUM(R14:R20)&gt;0),C32="",C5="",C5&lt;=0),"",C32/C5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="C34" s="26">
+        <f>IF(OR((SUM(R14:R20)&gt;0),C33="",C5="",C5&lt;=0),"",C33/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Worst case at peak (tokens per minute)</t>
         </is>
       </c>
-      <c r="C34" s="27">
-        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C32="",C7=""),"",C7*C32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="C35" s="27">
+        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C33="",C7=""),"",C7*C33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>…as a share of your quota</t>
         </is>
       </c>
-      <c r="C35" s="28">
-        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C34="",C8="",C8&lt;=0),"",C34/C8))</f>
-        <v/>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="C36" s="28">
+        <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C35="",C8="",C8&lt;=0),"",C35/C8))</f>
+        <v/>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Over 100% means this workflow alone would ask for more than the pool holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>Cost per task</t>
-        </is>
-      </c>
-      <c r="C36" s="29">
-        <f>IF(OR(C28="",C25=""),"",C28*C25/1000000)</f>
-        <v/>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
+          <t>Cost per task</t>
+        </is>
+      </c>
+      <c r="C37" s="29">
+        <f>IF(OR(C29="",C25=""),"",C29*C25/1000000)</f>
+        <v/>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
           <t>Cost per 1,000 tasks</t>
         </is>
       </c>
-      <c r="C37" s="29">
-        <f>IF(C36="","",C36*1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="C38" s="29">
+        <f>IF(C37="","",C37*1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>…in</t>
+        </is>
+      </c>
+      <c r="C39" s="7">
+        <f>IF(C37="","",IF(C26="","your own currency",C26))</f>
+        <v/>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Whatever you called your currency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>The five checks</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Pass — nothing to do here.   ·   Attention — it works today, and something about it will surprise you.   ·   Fail — this is the one that stops you scaling, fix it first.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="30" t="n"/>
-      <c r="J40" s="30" t="n"/>
-      <c r="K40" s="30" t="n"/>
-    </row>
-    <row r="41" ht="76" customHeight="1">
-      <c r="A41" s="31" t="n">
+      <c r="H41" s="30" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="76" customHeight="1">
+      <c r="A42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>Every path that sends work back is listed
 A path you have not listed is spend you cannot see. Most teams count their retries and miss the judge entirely, because a judge rejection looks like normal operation rather than a failure.</t>
         </is>
       </c>
-      <c r="F41" s="33">
+      <c r="F42" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G42" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back.")))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.","")))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.",""))))</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="76" customHeight="1">
-      <c r="A42" s="31" t="n">
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Each round is costed as repeated, review and growth
 A round is three things and teams usually count only the first. The review call and the growing context are what make a judge loop expensive, and neither appears in a retry counter.</t>
         </is>
       </c>
-      <c r="F42" s="33">
+      <c r="F43" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G43" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round."))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.",""))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.","")))))</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="76" customHeight="1">
-      <c r="A43" s="31" t="n">
+    <row r="44" ht="76" customHeight="1">
+      <c r="A44" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>Every loop has a limit, a decided outcome, and an owner
 A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
         </is>
       </c>
-      <c r="F43" s="33">
+      <c r="F44" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G44" s="14">
         <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner.")))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.","")))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.",""))))))</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="76" customHeight="1">
-      <c r="A44" s="31" t="n">
+    <row r="45" ht="76" customHeight="1">
+      <c r="A45" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>Both numbers fit: what you pay daily, and your busiest minute
 One number is not enough, because the two ways this hurts you are different. The typical cost is what you pay every day, and it decides whether the product makes money. The worst case at peak decides whether one bad minute takes the whole system down. A workflow can be fine on one and fatal on the other.</t>
         </is>
       </c>
-      <c r="F44" s="33">
-        <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
-        <v/>
-      </c>
-      <c r="G44" s="14">
-        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="76" customHeight="1">
-      <c r="A45" s="31" t="n">
+      <c r="F45" s="33">
+        <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C32="",C36=""),"Not answered",IF(C32&gt;1,"Fail",IF(AND(C32&lt;=0.8,C36&lt;=1),"Pass","Attention"))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="14">
+        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C32="",C36=""),"Peak tasks per minute and the quota are needed for this one.",IF(C32&gt;1,"Your normal load already exceeds the quota.",IF(AND(C32&lt;=0.8,C36&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C32&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C32="",C36=""),"",IF(C32&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C32&lt;=0.8,C36&lt;=1),"",IF(C32&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C32="",C36=""),"",IF(C32&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C32&lt;=0.8,C36&lt;=1),"",IF(C32&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>One token budget for the whole task, not one per call
 A task that goes round three times spends three times. A budget checked on each call sees the attempts one at a time and never sees the total, so it cannot stop a task that is running away. To do that, every round has to count against one limit that belongs to the task.</t>
         </is>
       </c>
-      <c r="F45" s="33">
-        <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
-        <v/>
-      </c>
-      <c r="G45" s="14">
-        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="52" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="F46" s="33">
+        <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C29=""),"Not answered",IF(C23&lt;C29,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"Pass",IF(C33="","Not answered","Attention"))))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
+        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C29=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C29,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C33="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C29=""),"",IF(C23&lt;C29,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"",IF(C33="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C29=""),"",IF(C23&lt;C29,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C33&lt;&gt;"",C33&lt;&gt;"Unbounded",C33&gt;C23)),"",IF(C33="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>Your next step</t>
         </is>
       </c>
-      <c r="C47" s="6">
-        <f>IF(COUNTIF(F41:F45,"Fail")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Fail",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Fail",F41:F45,0)),IF(COUNTIF(F41:F45,"Attention")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Attention",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Attention",F41:F45,0)),"Nothing outstanding."))</f>
+      <c r="C48" s="6">
+        <f>IF(COUNTIF(F42:F46,"Fail")&gt;0,"Check "&amp;INDEX(A42:A46,MATCH("Fail",F42:F46,0))&amp;" — "&amp;INDEX(G42:G46,MATCH("Fail",F42:F46,0)),IF(COUNTIF(F42:F46,"Attention")&gt;0,"Check "&amp;INDEX(A42:A46,MATCH("Attention",F42:F46,0))&amp;" — "&amp;INDEX(G42:G46,MATCH("Attention",F42:F46,0)),"Nothing outstanding."))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="56">
-    <mergeCell ref="C47:K47"/>
+  <mergeCells count="61">
     <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="E36:K36"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E26:K26"/>
     <mergeCell ref="G43:K43"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C40:K40"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="E32:K32"/>
     <mergeCell ref="E25:K25"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E37:K37"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="C29:D29"/>
@@ -3723,38 +3942,42 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C48:K48"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E39:K39"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="D7:K7"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="E29:K29"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="E35:K35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="G45:K45"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="B42:E42"/>
+    <mergeCell ref="C39:D39"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="E31:K31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="D8:K8"/>
     <mergeCell ref="E30:K30"/>
     <mergeCell ref="B44:E44"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="G44:K44"/>
     <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G44:K44"/>
     <mergeCell ref="D5:K5"/>
+    <mergeCell ref="G46:K46"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="A14:K20">
@@ -3762,15 +3985,15 @@
       <formula>$B14&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F45">
+  <conditionalFormatting sqref="F42:F46">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$F41="Pass"</formula>
+      <formula>$F42="Pass"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$F41="Attention"</formula>
+      <formula>$F42="Attention"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>$F41="Fail"</formula>
+      <formula>$F42="Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
